--- a/dk17.xlsx
+++ b/dk17.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\자리배치도_최신본\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344B2E3D-1078-4D24-8C14-8A55CC44918D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89A1979-E801-4628-8B46-BA6AAC7EED96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10320" yWindow="-17400" windowWidth="16410" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dk17" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="110">
   <si>
     <t/>
   </si>
@@ -135,6 +135,9 @@
 B</t>
   </si>
   <si>
+    <t>이민희</t>
+  </si>
+  <si>
     <t>박기연</t>
   </si>
   <si>
@@ -259,9 +262,6 @@
     <t>허진서</t>
   </si>
   <si>
-    <t>최보람</t>
-  </si>
-  <si>
     <t>최미정</t>
   </si>
   <si>
@@ -355,7 +355,7 @@
     <t>정종범</t>
   </si>
   <si>
-    <t>이민희</t>
+    <t>윤현일</t>
     <phoneticPr fontId="77" type="noConversion"/>
   </si>
 </sst>
@@ -6852,41 +6852,41 @@
       <c r="F29" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="G29" s="83" t="s">
-        <v>109</v>
+      <c r="G29" s="66" t="s">
+        <v>36</v>
       </c>
       <c r="J29" s="66" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K29" s="66" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N29" s="66" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O29" s="66" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R29" s="66" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S29" s="66" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V29" s="66" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W29" s="66" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Z29" s="66" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA29" s="66" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AD29" s="66" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE29" s="66" t="s">
         <v>0</v>
@@ -6898,19 +6898,19 @@
         <v>0</v>
       </c>
       <c r="AK29" s="66" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AL29" s="66" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AO29" s="66" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AP29" s="66" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AS29" s="66" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AT29" s="66" t="s">
         <v>0</v>
@@ -7123,46 +7123,46 @@
         <v>0</v>
       </c>
       <c r="C32" s="66" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F32" s="66" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G32" s="66" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J32" s="66" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K32" s="66" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N32" s="66" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O32" s="66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R32" s="66" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S32" s="66" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V32" s="66" t="s">
         <v>0</v>
       </c>
       <c r="W32" s="66" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z32" s="66" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA32" s="66" t="s">
         <v>0</v>
       </c>
       <c r="AD32" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AE32" s="66" t="s">
         <v>0</v>
@@ -7174,34 +7174,34 @@
         <v>0</v>
       </c>
       <c r="AK32" s="66" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AL32" s="66" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AO32" s="66" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AP32" s="66" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AS32" s="66" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AT32" s="66" t="s">
         <v>0</v>
       </c>
       <c r="AW32" s="66" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AX32" s="66" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="BA32" s="66" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="BB32" s="66" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="BE32" s="66" t="s">
         <v>0</v>
@@ -7405,28 +7405,26 @@
         <v>0</v>
       </c>
       <c r="C35" s="66" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F35" s="66" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G35" s="66" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J35" s="66" t="s">
-        <v>76</v>
-      </c>
-      <c r="K35" s="66" t="s">
         <v>77</v>
       </c>
+      <c r="K35" s="83"/>
       <c r="N35" s="66" t="s">
         <v>78</v>
       </c>
       <c r="O35" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="R35" s="66" t="s">
-        <v>0</v>
+      <c r="R35" s="83" t="s">
+        <v>109</v>
       </c>
       <c r="S35" s="66" t="s">
         <v>80</v>
@@ -7511,18 +7509,14 @@
       <c r="J36" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="K36" s="67" t="s">
-        <v>0</v>
-      </c>
+      <c r="K36" s="67"/>
       <c r="N36" s="67" t="s">
         <v>0</v>
       </c>
       <c r="O36" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="R36" s="67" t="s">
-        <v>0</v>
-      </c>
+      <c r="R36" s="67"/>
       <c r="S36" s="67" t="s">
         <v>0</v>
       </c>
@@ -7603,18 +7597,14 @@
       <c r="J37" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="K37" s="68" t="s">
-        <v>0</v>
-      </c>
+      <c r="K37" s="68"/>
       <c r="N37" s="68" t="s">
         <v>0</v>
       </c>
       <c r="O37" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="R37" s="68" t="s">
-        <v>0</v>
-      </c>
+      <c r="R37" s="68"/>
       <c r="S37" s="68" t="s">
         <v>0</v>
       </c>
@@ -8266,7 +8256,7 @@
   <phoneticPr fontId="77" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:CV28 A30:CV75 A29:F29 H29:CV29" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:CV34 A38:CV75 A35:J37 L35:Q37 S35:CV37" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>